--- a/outputs/019f6c42-2d53-7743-ab07-6293e2618dd7/k3_calibrated_frontier_parameter_crosscheck_2026-07-17.xlsx
+++ b/outputs/019f6c42-2d53-7743-ab07-6293e2618dd7/k3_calibrated_frontier_parameter_crosscheck_2026-07-17.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="R5162fa6bde44499a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revised Estimates" sheetId="2" r:id="R58a2f145a02043af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="K3 Validation" sheetId="3" r:id="R78ba522c12b845b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method Audit" sheetId="4" r:id="R4b8425ab61094a16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="Rff3f6dc08236481a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" r:id="R89498838a8ed4fe0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revised Estimates" sheetId="2" r:id="R5702173fb4264efe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="K3 Validation" sheetId="3" r:id="R9880d53ef1d74b1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method Audit" sheetId="4" r:id="R73da989f166b4fbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="5" r:id="R8553185fe3204108"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,7 +14,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={47D45B91-4DD6-62DE-F431-4528BD6AE581}</x:author>
+    <x:author>tc={7B02935A-7741-9F40-0B94-A7580109A714}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="I9" authorId="0">
@@ -34,8 +34,8 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={BA67A6C9-33C7-D69F-9581-4DDC2F43197B}</x:author>
-    <x:author>tc={04EAD1A0-D607-77F3-D1B1-202638518D7A}</x:author>
+    <x:author>tc={33B6C50E-24B5-3834-B854-740FFD61BD48}</x:author>
+    <x:author>tc={A274BFFB-8599-C129-B63C-CC7383202CC5}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="B14" authorId="0">
@@ -65,7 +65,7 @@
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={99855A03-71C8-EE00-CDE9-7668F9E08137}</x:author>
+    <x:author>tc={6742B623-FBEE-B1F6-50A4-1F636E7E4A2A}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="B18" authorId="0">
@@ -582,7 +582,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R476f9fbb69264514"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdec46b3170d14061"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -593,7 +593,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Codex" id="{F0EFBA1A-4D7F-421D-A367-DCD37EB609C6}"/>
+  <xltc:person displayName="Codex" id="{C68B0540-41C0-435C-9747-CADCB06BF0F6}"/>
 </xltc:personList>
 </file>
 
@@ -824,7 +824,7 @@
 
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="I9" dT="2026-08-01T16:01:57.874" personId="{F0EFBA1A-4D7F-421D-A367-DCD37EB609C6}" id="{47D45B91-4DD6-62DE-F431-4528BD6AE581}">
+  <xltc:threadedComment ref="I9" dT="2026-08-01T18:06:34.247" personId="{C68B0540-41C0-435C-9747-CADCB06BF0F6}" id="{7B02935A-7741-9F40-0B94-A7580109A714}">
     <xltc:text>K3 is the disclosed calibration anchor. It is not a regression estimate and therefore has no factor band in this workbook.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -832,10 +832,10 @@
 
 <file path=xl/threadedcomments/threadedcomment2.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="B14" dT="2026-08-01T16:01:57.874" personId="{F0EFBA1A-4D7F-421D-A367-DCD37EB609C6}" id="{BA67A6C9-33C7-D69F-9581-4DDC2F43197B}">
+  <xltc:threadedComment ref="B14" dT="2026-08-01T18:06:34.246" personId="{C68B0540-41C0-435C-9747-CADCB06BF0F6}" id="{33B6C50E-24B5-3834-B854-740FFD61BD48}">
     <xltc:text>This stricter prediction refits after removing all earlier Kimi-family rows, reducing same-lab leakage. It is still not fully independent of broader MoE design trends.</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="B19" dT="2026-08-01T16:01:57.874" personId="{F0EFBA1A-4D7F-421D-A367-DCD37EB609C6}" id="{04EAD1A0-D607-77F3-D1B1-202638518D7A}">
+  <xltc:threadedComment ref="B19" dT="2026-08-01T18:06:34.246" personId="{C68B0540-41C0-435C-9747-CADCB06BF0F6}" id="{A274BFFB-8599-C129-B63C-CC7383202CC5}">
     <xltc:text>This is a genuine check of the supplied workbook's frozen direct ECI equations against an ECI observation that was not present when those equations were recorded. It remains only one target and is not used to tune the branch weight.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -843,7 +843,7 @@
 
 <file path=xl/threadedcomments/threadedcomment3.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="B18" dT="2026-08-01T16:01:57.874" personId="{F0EFBA1A-4D7F-421D-A367-DCD37EB609C6}" id="{99855A03-71C8-EE00-CDE9-7668F9E08137}">
+  <xltc:threadedComment ref="B18" dT="2026-08-01T18:06:34.246" personId="{C68B0540-41C0-435C-9747-CADCB06BF0F6}" id="{6742B623-FBEE-B1F6-50A4-1F636E7E4A2A}">
     <xltc:text>No-date receives more weight because the date coefficient is unstable and the no-date row-LOO RMSE is better. The dated model remains in the ensemble so chronology is considered rather than discarded.</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
@@ -1414,7 +1414,7 @@
     <x:mergeCell ref="A34:P36"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R497017e05d0448e3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3d84ebee2304263"/>
 </x:worksheet>
 </file>
 
@@ -2203,9 +2203,9 @@
     <x:cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Kimi K3"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff30aacee78d4d30"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree7237178fe940ff"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf793a05c93d4b3e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9a7b8fb28cf405a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2462,7 +2462,7 @@
     <x:mergeCell ref="A23:H25"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16180eab2d9c4dd1"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a586c0484f04eb0"/>
 </x:worksheet>
 </file>
 
@@ -2883,7 +2883,7 @@
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="High"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f8a3ad7e6dd455f"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0221f785d6ce41da"/>
 </x:worksheet>
 </file>
 
@@ -3080,7 +3080,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a20895f1ddc4617"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R396e77d195b9447e"/>
   </x:tableParts>
 </x:worksheet>
 </file>